--- a/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_01_19_Cau.xlsx
+++ b/TONG_HOP_QUIZ_15_NGAY_EXCEL/02_FULL_NGAN_HANG_1679_CAU_CHI_TIET_CHIA_20_CAU/Day_10_Full_112_Cau/Day_10_Ngan_Hang_Phan_01_19_Cau.xlsx
@@ -624,10 +624,16 @@
       <c r="K3" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Giá trị lần đầu đổi khỏi nguồn đúng nằm ở artifact nào?
-Phân tích theo nguyên lý thiết kế: Giá trị lần đầu đổi khỏi nguồn đúng nằm ở artifact nào?</t>
+- [1.0 điểm] Xác định chính xác bước chuyển sai đầu tiên là từ manifest ingestion sang canonical artifact (bước cleaning/transformation).
+- [1.5 điểm] Phân tích bằng chứng đối soát dữ liệu (data lineage audit) giữa các artifact để loại trừ nguyên nhân từ nguồn gốc và chứng minh tầng sau chỉ là cascading error.
+- [1.5 điểm] Nêu rõ bước kiểm tra cụ thể tiếp theo: soi code/rule biến đổi của cleaning pipeline và chạy test case cô lập với payload mẫu 2026.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lần chuyển dữ liệu sai đầu tiên có bằng chứng: Bước chuyển từ 'manifest ingestion' (ghi đúng 2026) sang 'dòng canonical sau cleaning' (bị đổi thành 2025). Bằng chứng cụ thể là artifact manifest ingestion vẫn lưu giá trị 2026 khớp với bản ghi nguồn, nhưng ngay tại đầu ra của cleaning stage (canonical dataset), trường policy_version đã bị ghi đè/biến đổi thành 2025. Các giai đoạn index, retrieval và câu trả lời của agent chỉ là cascading failure kế thừa dữ liệu sai từ canonical artifact.
+2. Bước kiểm tra tiếp theo để xác nhận: Kiểm tra mã nguồn và bộ rule biến đổi (transformation/normalization script) của giai đoạn cleaning, cụ thể là các hàm parse date/regex hoặc hardcoded default value đối với policy_version; đồng thời chạy unit test tái hiện (regression test) với input payload chứa 'policy_version=2026' qua hàm clean để xác nhận logic nào đã biến đổi 2026 thành 2025.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kiến trúc Data Pipeline cho hệ thống RAG/Agent, lỗi Data Cascade xảy ra khi một khiếm khuyết dữ liệu ở tầng sớm lan truyền không kiểm soát xuống các tầng sau (vector index, retrieval chunk, LLM answer). Để định vị điểm lỗi gốc (root cause localization), nguyên lý bất biến là đối soát từng artifact trung gian theo thứ tự thời gian và lineage: nguồn gốc (2026) -&gt; manifest ingestion (2026) -&gt; canonical cleaning (2025). Sự chênh lệch (diff) đầu tiên xuất hiện tại đầu ra của cleaning, chứng minh bước làm sạch dữ liệu đã áp dụng phép biến đổi sai lệch hoặc áp dụng sai logic fallback/lookup.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE / Data Quality Fundamentals - Root Cause Analysis in Data Cascades: https://sre.google/sre-book/postmortem-culture/ và Great Expectations Data Contract Standards: https://docs.greatexpectations.io/</t>
         </is>
       </c>
     </row>
@@ -797,10 +803,17 @@
       <c r="K7" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Ai kiểm soát commit boundary và tài liệu nào chứng minh nó đã đổi?
-Phân tích theo nguyên lý thiết kế: Ai kiểm soát commit boundary và tài liệu nào chứng minh nó đã đổi?</t>
+- [1.0 điểm] Gán đúng vai trò chịu trách nhiệm (Data Platform Ops / Release Engineer / Serving Owner) có thẩm quyền kiểm soát commit boundary.
+- [1.5 điểm] Chỉ định rõ artifact bằng chứng (Deployment Audit Log / Alias Mapping Manifest / GitOps PR) ghi nhận sự kiện chuyển đổi.
+- [1.5 điểm] Thiết lập đầy đủ điều kiện chấp nhận bàn giao: runbook rõ ràng, kiểm thử phân giải alias tự động và ký duyệt nghiệm thu giữa các bên.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Vai trò chịu trách nhiệm: Release Manager / Data Platform Ops (kỹ sư vận hành đường ống dữ liệu phục vụ model/serving). Vai trò này chịu trách nhiệm quản lý commit boundary của serving layer và kiểm soát định tuyến alias giữa các snapshot.
+2. Artifact bằng chứng: Bản ghi triển khai hoặc lệnh switch alias có gắn audit trail (Deployment Manifest / Audit Log / GitOps PR), ghi rõ: commit hash, snapshot_id mới đã vượt qua quality checks, timestamp chuyển đổi, và danh tính người thực hiện (hoặc service account thực thi CI/CD).
+3. Điều kiện chấp nhận bàn giao (Handover Acceptance Criteria): (a) Có tài liệu Runbook chuẩn hóa quy định rõ thẩm quyền và thủ tục switch alias; (b) Kiểm thử routing tự động xác nhận serving alias phân giải về đúng snapshot mới; (c) Bản ghi bàn giao có chữ ký/phê duyệt của Data Lead và ML Serving Lead trước khi đóng incident.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Sự cố 'canonical data đã đạt chuẩn nhưng serving alias vẫn trỏ vào snapshot cũ' là vấn đề điển hình của việc thiếu ranh giới trách nhiệm (RACI) và thiếu cơ chế chuyển giao nguyên tử (atomic cutover). Trong kiến trúc phục vụ dữ liệu, việc tạo ra snapshot sạch và việc chuyển hướng traffic (alias pointer swap) phải được phân tách rõ ràng. Người nắm giữ quyền commit boundary phải cung cấp bằng chứng bất biến (immutable deployment record) và tuân thủ tiêu chí chấp nhận bàn giao để tránh tình trạng dữ liệu mồ côi hoặc không rõ ai có thẩm quyền kích hoạt.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Martin Kleppmann, Designing Data-Intensive Applications (O'Reilly) - Dataflow, Immutability &amp; Serving Layer Boundaries; Google Cloud Architecture Framework: https://cloud.google.com/architecture/framework</t>
         </is>
       </c>
     </row>
@@ -831,10 +844,30 @@
       <c r="K8" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Mỗi dòng phải trả lời signal nào sẽ đổi khi failure đó xảy ra.
-Phân tích theo nguyên lý thiết kế: Mỗi dòng phải trả lời signal nào sẽ đổi khi failure đó xảy ra.</t>
+- [1.0 điểm] Thiết lập đầy đủ bản đồ cho 3 nguồn với cấu trúc method -&gt; failure -&gt; monitor -&gt; owner rõ ràng.
+- [1.5 điểm] Chỉ số giám sát (monitor) phân biệt chính xác đặc trưng hỏng hóc của từng nguồn (file size/freshness cho DB, HTTP 429 rate cho API, confidence/structure cho OCR).
+- [1.5 điểm] Phân định vai trò owner chuyên môn hóa tương ứng cho từng nguồn, tránh dồn chung trách nhiệm mơ hồ.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Bản đồ method -&gt; failure -&gt; monitor -&gt; owner:
+1. DB snapshot hằng đêm:
+   - Method: Batch export / Snapshot dump từ cơ sở dữ liệu nguồn.
+   - Failure: Snapshot bị chậm/trễ (stale data), thiếu dữ liệu (missing rows), hoặc dump file bị hỏng (corrupted dump).
+   - Monitor: Kiểm tra kích thước file dump (size threshold), số lượng bản ghi (record count check), và độ trễ snapshot so với thời gian chốt (freshness timestamp alert).
+   - Owner: Database Administrator (DBA) / Core Data Engineering Team.
+2. API phân trang có 429:
+   - Method: HTTP REST pagination ingestion (offset/cursor-based).
+   - Failure: Rate limiting (HTTP 429 Too Many Requests), cạn kiệt hạn ngạch (quota exhaustion) hoặc rớt kết nối giữa các page.
+   - Monitor: Tỷ lệ mã phản hồi HTTP 429/5xx (API error rate metric), số lần retry vượt ngưỡng và consumer backoff time qua OpenTelemetry HTTP metrics.
+   - Owner: Integration Engineer / Ingestion Pipeline Team.
+3. Thư mục PDF có OCR:
+   - Method: File watcher / Object storage ingestion kết hợp pipeline OCR parsing.
+   - Failure: OCR parsing failure, font encoding lỗi, trích xuất thiếu bảng biểu (table structure loss) hoặc điểm tin cậy thấp (low confidence score &lt; 0.8).
+   - Monitor: Tỷ lệ tài liệu có OCR confidence score thấp, phân phối độ dài văn bản sau OCR và số lượng file rơi vào thư mục lỗi / quarantine queue.
+   - Owner: Unstructured Data / ML Data Preparation Team.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mỗi phương thức thu nạp (ingestion method) có các cơ chế lỗi (failure mode) vật lý và logic hoàn toàn khác biệt. Việc giám sát không thể dùng chung một chỉ số tổng thể mà phải dựa trên tín hiệu đặc trưng (characteristic signal) của lỗi đó: DB snapshot phụ thuộc vào tính toàn vẹn và độ tươi của file; API phụ thuộc vào giao thức mạng và rate limit; OCR phụ thuộc vào chất lượng thị giác và điểm tin cậy mô hình. Gán owner chính xác đảm bảo khi alert kích hoạt, đúng kỹ sư chuyên trách sẽ nhận sự cố để xử lý kịp thời theo SLA.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+OpenTelemetry Instrumentation Standards for Ingestion Pipelines: https://opentelemetry.io/docs/specs/semconv/ và SRE Workbook - Practical Alerting &amp; On-Call: https://sre.google/workbook/alerting-on-slos/</t>
         </is>
       </c>
     </row>
@@ -865,10 +898,24 @@
       <c r="K9" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Với từng dòng, hỏi signal nào thật sự thay đổi khi failure đã mô tả xảy ra.
-Phân tích theo nguyên lý thiết kế: Với từng dòng, hỏi signal nào thật sự thay đổi khi failure đã mô tả xảy ra.</t>
+- [1.0 điểm] Chỉ ra đúng lỗi sai bản chất của cả 3 dòng trong bản đồ nháp (CPU proxy, name vs checksum, unowned alert).
+- [1.5 điểm] Đề xuất monitor thay thế chính xác: Consumer Group Lag cho stream, Checksum/ETag/Versioning cho object storage, Partition completeness schedule cho SaaS.
+- [1.5 điểm] Gán owner chịu trách nhiệm cụ thể và rõ ràng cho từng loại giám sát, đảm bảo tính khả thi vận hành.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+Chỉ ra lỗi và hiệu chỉnh cho từng dòng:
+1. Dòng (1) - Event stream có consumer lag nhưng chỉ theo dõi CPU của worker:
+   - Lỗi: CPU worker cao hay thấp không phản ánh trực tiếp tình trạng tồn đọng message. Worker có thể CPU thấp do bị deadlock, nghẽn I/O, hoặc CPU cao nhưng vẫn xử lý kịp.
+   - Sửa: Monitor trực tiếp chỉ số 'Consumer Group Lag' (số lượng offset chênh lệch giữa latest log end offset và committed consumer offset) trên Kafka/RabbitMQ. Owner: Streaming Platform Team / Event Pipeline Engineer.
+2. Dòng (2) - Object storage nhận file trùng tên nhưng chỉ theo dõi tên file:
+   - Lỗi: Tên file trùng nhau là trạng thái bình thường nếu có cập nhật phiên bản, nhưng chỉ theo dõi tên file không thể phát hiện ghi đè dữ liệu ngoài ý muốn (silent overwrite) hoặc race condition.
+   - Sửa: Monitor trường Content-MD5 / ETag checksum và kích hoạt Object Versioning; cảnh báo khi phát hiện checksum khác nhau cùng một key name hoặc xuất hiện event 's3:ObjectCreated:Put' ghi đè lên file đang được pipeline đọc. Owner: Data Lakehouse Storage Admin / Data Ingestion Team.
+3. Dòng (3) - SaaS export thỉnh thoảng thiếu partition nhưng alert không có owner:
+   - Lỗi: Cảnh báo không có người nhận (unowned alert) sẽ dẫn đến việc alert fatigue hoặc bị lờ đi hoàn toàn, vi phạm nguyên tắc cơ bản của SRE.
+   - Sửa: Thiết lập monitor 'Partition Completeness Check' (kiểm tra sự tồn tại của partition timestamp theo lịch hẹn) và định tuyến alert vào PagerDuty/Slack on-call cụ thể: SaaS Integration Engineer / Partner Data On-call Team.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc cốt lõi của Observability trong hệ thống dữ liệu là 'theo dõi tín hiệu phản ánh trực tiếp trạng thái hư hỏng' (direct failure signal) thay vì chỉ số proxy gián tiếp. Consumer lag là thước đo trực tiếp của streaming bottleneck; Checksum/versioning là thước đo của xung đột lưu trữ; và bất kỳ alert nào sinh ra cũng phải có một 'On-Call Owner' với runbook xử lý tương ứng để chuyển hóa cảnh báo thành hành động khắc phục.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Google SRE Book - Monitoring Distributed Systems: https://sre.google/sre-book/monitoring-distributed-systems/ và Apache Kafka Consumer Lag Monitoring: https://kafka.apache.org/documentation/#monitoring</t>
         </is>
       </c>
     </row>
@@ -1039,10 +1086,21 @@
       <c r="K13" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Rule đổi nhanh và replay cần input gốc, nhưng raw vẫn phải có boundary.
-Phân tích theo nguyên lý thiết kế: Rule đổi nhanh và replay cần input gốc, nhưng raw vẫn phải có boundary.</t>
+- [1.0 điểm] Lựa chọn chính xác kiến trúc ELT và giải thích lý do thuyết phục dựa trên compute mạnh, rule đổi hàng tuần và yêu cầu audit.
+- [1.5 điểm] Bố trí chuẩn xác vị trí Raw Data (Bronze/Object storage immutable) và Transformation Logic (Silver/dbt/code versioned).
+- [1.5 điểm] Thiết lập ít nhất 2 guardrail quan trọng: ranh giới cấm Agent truy cập trực tiếp Raw zone và chính sách bảo toàn dữ liệu thô (WORM/immutability).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Lựa chọn kiến trúc: Chọn ELT (Extract - Load - Transform). Lý do: Target lakehouse sở hữu năng lực compute mạnh mẽ, quy tắc nghiệp vụ biến động hàng tuần và yêu cầu audit bắt buộc phải replay lại từ input gốc. ELT cho phép nạp nguyên vẹn dữ liệu thô vào vùng Raw trước, sau đó dùng compute của Lakehouse chạy các script chuyển đổi (dbt/Spark/SQL) linh hoạt theo từng phiên bản rule.
+2. Vị trí lưu trữ Raw Data và Transformation Logic:
+   - Raw Data: Đặt tại vùng đệm 'Raw Zone / Bronze Layer' trên Object Storage của Lakehouse (bất biến - immutable, append-only, lưu kèm ingestion timestamp, source system, và raw payload).
+   - Transformation Logic: Đặt tại tầng 'Silver Layer' của Lakehouse, được mã hóa dưới dạng code (dbt models / Spark transformations có version control bằng Git), chạy định kỳ hoặc theo sự kiện để sinh ra dữ liệu Canonical.
+3. Guardrails cần thiết:
+   - Guardrail 1 (Access Control Boundary): Phân quyền nghiêm ngặt (IAM / RBAC) chặn hoàn toàn quyền đọc trực tiếp của RAG Agent vào Raw Zone; agent chỉ được phép đọc từ Curated/Gold serving table.
+   - Guardrail 2 (Immutability &amp; Replayability Guard): Raw Zone được bật tính năng Write Once Read Many (WORM) hoặc bucket object lock để đảm bảo phục vụ audit và replay mà không bị sửa đổi lịch sử.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Mô hình ELT vượt trội hơn ETL truyền thống khi hạ tầng đích có compute có khả năng scale tốt và yêu cầu nghiệp vụ thay đổi thường xuyên. Trong ETL, việc chuyển đổi trước khi lưu trữ làm mất cấu trúc nguyên bản, khiến việc thay đổi rule đòi hỏi phải trích xuất lại từ source gốc (thường tốn kém hoặc bất khả thi). Với ELT, Raw Zone đóng vai trò là 'Source of Truth bất biến', cho phép tính toán lại lịch sử (replay) bất kỳ lúc nào. Tuy nhiên, ranh giới an toàn (guardrail) phân tầng là bắt buộc để ngăn chặn các truy vấn RAG vô tình lấy nhầm dữ liệu thô chưa làm sạch hoặc dữ liệu chứa thông tin nhạy cảm.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Databricks Medallion Architecture (Bronze-Silver-Gold design): https://www.databricks.com/glossary/medallion-architecture và dbt Labs Design Principles: https://docs.getdbt.com/terms/elt</t>
         </is>
       </c>
     </row>
@@ -1122,10 +1180,21 @@
       <c r="K15" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Một product có thể có hai consumer SLA khác nhau.
-Phân tích theo nguyên lý thiết kế: Một product có thể có hai consumer SLA khác nhau.</t>
+- [1.0 điểm] Thiết kế rõ ràng 2 luồng: Stream processing thời gian thực cho chặn gian lận (3s SLA) và Batch/Micro-batch cho dashboard (30m SLA).
+- [1.5 điểm] Xác định nền tảng log bền vững chung (Kafka/Kinesis) làm nguồn cung cấp dữ liệu duy nhất cho cả hai luồng.
+- [1.5 điểm] Trình bày đầy đủ cơ chế checkpoint độc lập theo consumer group và chính sách replay log (offset reset, log retention &gt;= 7 ngày).
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Thiết kế luồng (Hybrid Architecture trên cùng Durable Log):
+   - Nền tảng chung: Sử dụng một durable message log trung tâm (như Apache Kafka hoặc AWS Kinesis) lưu trữ toàn bộ event `OrderCreated` với retention time tối thiểu 7 ngày.
+   - Luồng chặn gian lận (Fraud Detection): Sử dụng Stream Processing (Kafka Streams / Flink / Lightweight Python consumer), consume trực tiếp từ topic orders theo real-time offset, thực thi rule/model suy luận trong vòng &lt; 500ms để trả kết quả chặn trước mốc 3 giây SLA.
+   - Luồng Dashboard (Business Reporting): Sử dụng Micro-batch / Batch Ingestion (ví dụ Kafka Connect S3 sink nạp parquet vào Data Lakehouse theo chu kỳ 15-30 phút), dashboard truy vấn trên dữ liệu aggregate hoàn tất.
+2. Checkpoint và Replay tối thiểu cần giữ:
+   - Checkpoint: Mỗi consumer group duy trì checkpoint offset độc lập được commit định kỳ (commit offset cho fraud group; Iceberg/Delta snapshot timestamp cho batch dashboard group).
+   - Replay Log: Durable log lưu trữ retention &gt;= 7 ngày. Khi có sự cố thuật toán gian lận hoặc logic dashboard, nhóm chỉ cần reset consumer offset về timestamp mong muốn trên topic để replay lại toàn bộ luồng mà không cần query lại database nghiệp vụ nguồn.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Trong kiến trúc hướng sự kiện (Kappa Architecture), một durable commit log duy nhất có thể phục vụ đồng thời nhiều consumer có Service Level Agreement (SLA) khác nhau: consumer nhạy cảm với độ trễ (real-time stream) và consumer hướng dung lượng lớn (batch analytics). Việc duy trì consumer offset độc lập trên cùng log đảm bảo hai luồng không ảnh hưởng tài nguyên lẫn nhau (bulkhead isolation) và cho phép khả năng phát lại sự kiện (replayability) tức thời khi cần kiểm thử hồi quy hoặc khôi phục dữ liệu.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Jay Kreps, 'Questioning the Lambda Architecture' (O'Reilly / Confluent): https://www.oreilly.com/radar/questioning-the-lambda-architecture/ và Apache Flink Checkpointing &amp; State Management: https://nightlies.apache.org/flink/flink-docs-stable/</t>
         </is>
       </c>
     </row>
@@ -1292,10 +1361,19 @@
       <c r="K19" s="3" t="inlineStr">
         <is>
           <t>👉 Tiêu chí chấm (Rubric 4 điểm):
-- Đúng bản chất vấn đề và yêu cầu kỹ thuật.
-- Đầy đủ các tiêu chí chấp nhận / test case tối thiểu.
-- Gợi ý cốt lõi: Tìm record đã seen nhưng chưa hoàn tất contract.
-Phân tích theo nguyên lý thiết kế: Tìm record đã seen nhưng chưa hoàn tất contract.</t>
+- [1.0 điểm] Chẩn đoán chính xác nguyên nhân data loss do watermark nhảy cóc qua dải bản ghi lỗi 151-175.
+- [1.5 điểm] Thiết kế lại checkpoint: chỉ commit đến bản ghi liên tục thành công (150) hoặc cô lập vào DLQ trước khi commit.
+- [1.5 điểm] Xây dựng cơ chế replay độc lập và định nghĩa tín hiệu dừng (stall signal / error rate threshold) khi gặp lỗi nghiêm trọng.
+CÂU TRẢ LỜI MẪU CHI TIẾT:
+1. Chẩn đoán data loss: Lỗi thuộc loại 'Unprocessed Record Skipping'. Run 08:00 xử lý dải 101-200, trong đó các bản ghi 151-175 bị fail validation (chưa được ghi thành công vào canonical store), nhưng pipeline vẫn cập nhật `last_synced_id=200`. Do đó, lần chạy tiếp theo bắt đầu từ 201, dẫn đến 25 bản ghi (151-175) bị bỏ qua vĩnh viễn (silent data drop), vi phạm nguyên tắc toàn vẹn dữ liệu.
+2. Thiết kế checkpoint đúng: Checkpoint `last_synced_id` chỉ được tăng đến bản ghi liên tục thành công lớn nhất (high watermark of contiguous processed records), ở đây là `150`. Các bản ghi lỗi từ 151-175 phải được đẩy vào Quarantine / Dead Letter Queue (DLQ) kèm error payload.
+3. Thiết kế Replay và Stall Signal:
+   - Replay: Cơ chế replay riêng cho dải lỗi (DLQ re-drive) sau khi sửa rule hoặc data; hoặc nếu batch mang tính atomic thì rollback toàn bộ batch 101-200 và chạy lại từ 101.
+   - Stall Signal: Khi tỷ lệ lỗi vượt ngưỡng (ở đây 25/100 = 25% fail), pipeline phải phát tín hiệu Stall Alert (Hard Gate Stop), dừng tiến trình sync tự động và báo động cho On-call Engineer thay vì âm thầm nhảy watermark.
+PHÂN TÍCH THEO NGUYÊN LÝ THIẾT KẾ:
+Nguyên tắc cơ bản của Watermarking và Checkpointing trong xử lý dữ liệu tuần tự là: 'Không bao giờ được đẩy watermark vượt qua bản ghi chưa hoàn tất hợp đồng (uncommitted / failed record)'. Nếu pipeline gặp lỗi nhưng vẫn cập nhật high-watermark theo ID lớn nhất đã đọc thay vì ID lớn nhất đã xử lý thành công, toàn bộ dữ liệu lỗi ở giữa sẽ bị mất dấu (lost window). Phải tách biệt rõ ràng giữa read-watermark và commit-watermark, kết hợp với DLQ để cô lập lỗi.
+NGUỒN THAM KHẢO &amp; TÀI LIỆU KỸ THUẬT:
+Apache Kafka Offset Management &amp; Exactly-Once Semantics: https://kafka.apache.org/documentation/#semantics và Tyler Akidau et al., Streaming Systems (O'Reilly) - Watermarks &amp; Checkpointing: https://www.oreilly.com/library/view/streaming-systems/9781491983867/</t>
         </is>
       </c>
     </row>
